--- a/data processing/goFlux_reprocessing/ymf_black_oak/results/CO2_best_YMF.xlsx
+++ b/data processing/goFlux_reprocessing/ymf_black_oak/results/CO2_best_YMF.xlsx
@@ -647,7 +647,7 @@
         <v>43</v>
       </c>
       <c r="B2" t="n">
-        <v>1.09028443267916</v>
+        <v>1.07119650180274</v>
       </c>
       <c r="C2" t="n">
         <v>510.673383365281</v>
@@ -668,10 +668,10 @@
         <v>160.072921593051</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00596972543730537</v>
+        <v>0.00586521027203508</v>
       </c>
       <c r="J2" t="n">
-        <v>0.547538354063807</v>
+        <v>0.547538221247399</v>
       </c>
       <c r="K2" t="n">
         <v>0.998592889197321</v>
@@ -680,7 +680,7 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000184169642942053</v>
       </c>
       <c r="M2" t="n">
-        <v>1.14173417378919</v>
+        <v>1.12174549713261</v>
       </c>
       <c r="N2" t="n">
         <v>509.838274465561</v>
@@ -701,10 +701,10 @@
         <v>156.85545936672</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0231256794633355</v>
+        <v>0.0227208058663035</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02548719257355</v>
+        <v>2.02548670125105</v>
       </c>
       <c r="V2" t="n">
         <v>0.998747896186046</v>
@@ -719,13 +719,13 @@
         <v>618.822</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00198275712173584</v>
+        <v>0.00194804440847494</v>
       </c>
       <c r="AA2" t="n">
         <v>0.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.32973961803961</v>
+        <v>2.28895217995805</v>
       </c>
       <c r="AC2" t="n">
         <v>48</v>
@@ -746,7 +746,7 @@
         <v>45</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.14173417378919</v>
+        <v>1.12174549713261</v>
       </c>
       <c r="AJ2" t="s">
         <v>46</v>
@@ -770,7 +770,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="3">
@@ -778,7 +778,7 @@
         <v>48</v>
       </c>
       <c r="B3" t="n">
-        <v>1.27234696475888</v>
+        <v>1.2500716114784</v>
       </c>
       <c r="C3" t="n">
         <v>449.571145105911</v>
@@ -799,10 +799,10 @@
         <v>246.025389037854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00279467092543656</v>
+        <v>0.00274574398292672</v>
       </c>
       <c r="J3" t="n">
-        <v>0.219646920442505</v>
+        <v>0.219646935240731</v>
       </c>
       <c r="K3" t="n">
         <v>0.999633472356177</v>
@@ -811,7 +811,7 @@
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000796761925952472</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3307836151745</v>
+        <v>1.30748519423355</v>
       </c>
       <c r="N3" t="n">
         <v>448.025122126705</v>
@@ -832,10 +832,10 @@
         <v>210.688080667702</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00902115729583139</v>
+        <v>0.00886322183360238</v>
       </c>
       <c r="U3" t="n">
-        <v>0.677883105334784</v>
+        <v>0.677883151005622</v>
       </c>
       <c r="V3" t="n">
         <v>0.99977497116895</v>
@@ -850,13 +850,13 @@
         <v>652.585</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001229556229413</v>
+        <v>0.00120803002614691</v>
       </c>
       <c r="AA3" t="n">
         <v>0.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.33000905473764</v>
+        <v>2.2892168995484</v>
       </c>
       <c r="AC3" t="n">
         <v>77</v>
@@ -877,7 +877,7 @@
         <v>45</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.3307836151745</v>
+        <v>1.30748519423355</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
@@ -909,7 +909,7 @@
         <v>49</v>
       </c>
       <c r="B4" t="n">
-        <v>1.01572817524315</v>
+        <v>0.997945522737853</v>
       </c>
       <c r="C4" t="n">
         <v>570.13579683447</v>
@@ -930,10 +930,10 @@
         <v>745.596707845521</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00260626905998306</v>
+        <v>0.00256064122916799</v>
       </c>
       <c r="J4" t="n">
-        <v>0.25659119472187</v>
+        <v>0.256591283875186</v>
       </c>
       <c r="K4" t="n">
         <v>0.999026524050469</v>
@@ -942,7 +942,7 @@
         <v>1.75082285571673e-223</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1261297916822</v>
+        <v>1.10641430554187</v>
       </c>
       <c r="N4" t="n">
         <v>564.491275687461</v>
@@ -963,10 +963,10 @@
         <v>533.0241986588</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00546760059623162</v>
+        <v>0.00537187956773167</v>
       </c>
       <c r="U4" t="n">
-        <v>0.485521352566669</v>
+        <v>0.485521521262398</v>
       </c>
       <c r="V4" t="n">
         <v>0.999769549580697</v>
@@ -981,13 +981,13 @@
         <v>885.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.000633902133824072</v>
+        <v>0.00062280422235237</v>
       </c>
       <c r="AA4" t="n">
         <v>0.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3359293631417</v>
+        <v>2.29503355936848</v>
       </c>
       <c r="AC4" t="n">
         <v>149</v>
@@ -1008,7 +1008,7 @@
         <v>45</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.1261297916822</v>
+        <v>1.10641430554187</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
@@ -1032,7 +1032,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.00063</v>
+        <v>0.00062</v>
       </c>
     </row>
     <row r="5">
@@ -1040,7 +1040,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1.12550151487279</v>
+        <v>1.10579702815972</v>
       </c>
       <c r="C5" t="n">
         <v>602.085227800366</v>
@@ -1061,10 +1061,10 @@
         <v>325.772821693478</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00704618108064478</v>
+        <v>0.00692282373586213</v>
       </c>
       <c r="J5" t="n">
-        <v>0.626048120551947</v>
+        <v>0.62604832166923</v>
       </c>
       <c r="K5" t="n">
         <v>0.997341812842276</v>
@@ -1073,7 +1073,7 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000313262631310563</v>
       </c>
       <c r="M5" t="n">
-        <v>1.20842158337</v>
+        <v>1.1872653905807</v>
       </c>
       <c r="N5" t="n">
         <v>600.135154243271</v>
@@ -1094,10 +1094,10 @@
         <v>317.823975957925</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0274791548306164</v>
+        <v>0.0269980778418222</v>
       </c>
       <c r="U5" t="n">
-        <v>2.27397087314375</v>
+        <v>2.27397160365445</v>
       </c>
       <c r="V5" t="n">
         <v>0.997707251307285</v>
@@ -1112,13 +1112,13 @@
         <v>766.692</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0013760043860827</v>
+        <v>0.00135191427177863</v>
       </c>
       <c r="AA5" t="n">
         <v>0.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.33232743441018</v>
+        <v>2.29149469066478</v>
       </c>
       <c r="AC5" t="n">
         <v>69</v>
@@ -1139,7 +1139,7 @@
         <v>45</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.20842158337</v>
+        <v>1.1872653905807</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
@@ -1171,7 +1171,7 @@
         <v>51</v>
       </c>
       <c r="B6" t="n">
-        <v>1.30314854895781</v>
+        <v>1.28033394326534</v>
       </c>
       <c r="C6" t="n">
         <v>475.296879705506</v>
@@ -1192,10 +1192,10 @@
         <v>140.067680438081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00240682241291168</v>
+        <v>0.00236468560074741</v>
       </c>
       <c r="J6" t="n">
-        <v>0.184692866736991</v>
+        <v>0.184692877447001</v>
       </c>
       <c r="K6" t="n">
         <v>0.999791962695814</v>
@@ -1204,7 +1204,7 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000218764550397031</v>
       </c>
       <c r="M6" t="n">
-        <v>1.32386833098952</v>
+        <v>1.30069097796678</v>
       </c>
       <c r="N6" t="n">
         <v>474.856541895539</v>
@@ -1225,10 +1225,10 @@
         <v>141.244244479952</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00956410405168127</v>
+        <v>0.00939666300834304</v>
       </c>
       <c r="U6" t="n">
-        <v>0.722436199114502</v>
+        <v>0.722436241007207</v>
       </c>
       <c r="V6" t="n">
         <v>0.999795764899988</v>
@@ -1243,13 +1243,13 @@
         <v>643.644</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00153549278999916</v>
+        <v>0.00150861046520551</v>
       </c>
       <c r="AA6" t="n">
         <v>0.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.33394904079873</v>
+        <v>2.29308790711238</v>
       </c>
       <c r="AC6" t="n">
         <v>62</v>
@@ -1270,7 +1270,7 @@
         <v>45</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.32386833098952</v>
+        <v>1.30069097796678</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
@@ -1302,7 +1302,7 @@
         <v>53</v>
       </c>
       <c r="B7" t="n">
-        <v>1.31933987276378</v>
+        <v>1.29624180079376</v>
       </c>
       <c r="C7" t="n">
         <v>543.867877567416</v>
@@ -1323,10 +1323,10 @@
         <v>339.165621088061</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00130063531391833</v>
+        <v>0.00127786476928609</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0985822789690826</v>
+        <v>0.0985822836837681</v>
       </c>
       <c r="K7" t="n">
         <v>0.999887278397298</v>
@@ -1335,7 +1335,7 @@
         <v>4.41442093026646e-229</v>
       </c>
       <c r="M7" t="n">
-        <v>1.34106207568664</v>
+        <v>1.31758370670838</v>
       </c>
       <c r="N7" t="n">
         <v>542.977314137407</v>
@@ -1356,10 +1356,10 @@
         <v>333.717226522434</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00508102779339611</v>
+        <v>0.00499207298115187</v>
       </c>
       <c r="U7" t="n">
-        <v>0.378880879976758</v>
+        <v>0.378880898096653</v>
       </c>
       <c r="V7" t="n">
         <v>0.999894443336438</v>
@@ -1374,13 +1374,13 @@
         <v>868.593</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.000807317640983459</v>
+        <v>0.000793183693121306</v>
       </c>
       <c r="AA7" t="n">
         <v>0.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.3331479824422</v>
+        <v>2.29230087312057</v>
       </c>
       <c r="AC7" t="n">
         <v>117</v>
@@ -1401,7 +1401,7 @@
         <v>45</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.34106207568664</v>
+        <v>1.31758370670838</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
@@ -1425,7 +1425,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.00081</v>
+        <v>0.00079</v>
       </c>
     </row>
     <row r="8">
@@ -1433,7 +1433,7 @@
         <v>54</v>
       </c>
       <c r="B8" t="n">
-        <v>0.932800122520638</v>
+        <v>0.916469315873757</v>
       </c>
       <c r="C8" t="n">
         <v>536.719264473797</v>
@@ -1454,10 +1454,10 @@
         <v>956.44108841516</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00323900865565536</v>
+        <v>0.00318230238234952</v>
       </c>
       <c r="J8" t="n">
-        <v>0.347235016104288</v>
+        <v>0.347235016735452</v>
       </c>
       <c r="K8" t="n">
         <v>0.998014485619764</v>
@@ -1466,7 +1466,7 @@
         <v>1.00781548562163e-223</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09834555739463</v>
+        <v>1.07911649803215</v>
       </c>
       <c r="N8" t="n">
         <v>527.388380071498</v>
@@ -1487,10 +1487,10 @@
         <v>517.809261917687</v>
       </c>
       <c r="T8" t="n">
-        <v>0.00387359138341507</v>
+        <v>0.00380577528441222</v>
       </c>
       <c r="U8" t="n">
-        <v>0.352675108242216</v>
+        <v>0.352675108883269</v>
       </c>
       <c r="V8" t="n">
         <v>0.999860422432155</v>
@@ -1505,13 +1505,13 @@
         <v>857.669</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.000567910694526141</v>
+        <v>0.00055796811463031</v>
       </c>
       <c r="AA8" t="n">
         <v>0.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.33411295450244</v>
+        <v>2.29324895113058</v>
       </c>
       <c r="AC8" t="n">
         <v>166</v>
@@ -1532,7 +1532,7 @@
         <v>45</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.09834555739463</v>
+        <v>1.07911649803215</v>
       </c>
       <c r="AJ8" t="s">
         <v>46</v>
@@ -1556,7 +1556,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00057</v>
+        <v>0.00056</v>
       </c>
     </row>
     <row r="9">
@@ -1564,7 +1564,7 @@
         <v>55</v>
       </c>
       <c r="B9" t="n">
-        <v>1.10063846684457</v>
+        <v>1.08136926484062</v>
       </c>
       <c r="C9" t="n">
         <v>487.872245865154</v>
@@ -1585,10 +1585,10 @@
         <v>1138.39096300744</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00283810804308744</v>
+        <v>0.00278842047449055</v>
       </c>
       <c r="J9" t="n">
-        <v>0.25786015377275</v>
+        <v>0.257860156114343</v>
       </c>
       <c r="K9" t="n">
         <v>0.998731607593589</v>
@@ -1597,7 +1597,7 @@
         <v>2.26349997370336e-277</v>
       </c>
       <c r="M9" t="n">
-        <v>1.25398474563604</v>
+        <v>1.2320308651372</v>
       </c>
       <c r="N9" t="n">
         <v>477.824153577128</v>
@@ -1618,10 +1618,10 @@
         <v>616.154368073799</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00318410846766207</v>
+        <v>0.00312836337075066</v>
       </c>
       <c r="U9" t="n">
-        <v>0.253919234563499</v>
+        <v>0.253919236869305</v>
       </c>
       <c r="V9" t="n">
         <v>0.9999173464781</v>
@@ -1636,13 +1636,13 @@
         <v>926.335</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.000491801324994015</v>
+        <v>0.00048319121426048</v>
       </c>
       <c r="AA9" t="n">
         <v>0.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.33605629372157</v>
+        <v>2.29515826773728</v>
       </c>
       <c r="AC9" t="n">
         <v>192</v>
@@ -1663,7 +1663,7 @@
         <v>45</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.25398474563604</v>
+        <v>1.2320308651372</v>
       </c>
       <c r="AJ9" t="s">
         <v>46</v>
@@ -1687,7 +1687,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.00049</v>
+        <v>0.00048</v>
       </c>
     </row>
     <row r="10">
@@ -1695,7 +1695,7 @@
         <v>56</v>
       </c>
       <c r="B10" t="n">
-        <v>1.26070021803685</v>
+        <v>1.2386287677836</v>
       </c>
       <c r="C10" t="n">
         <v>479.164038720243</v>
@@ -1716,10 +1716,10 @@
         <v>286.962165739618</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00256916690527676</v>
+        <v>0.00252418680633168</v>
       </c>
       <c r="J10" t="n">
-        <v>0.203788884028072</v>
+        <v>0.203788808397246</v>
       </c>
       <c r="K10" t="n">
         <v>0.999713524615498</v>
@@ -1728,7 +1728,7 @@
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000203962851563755</v>
       </c>
       <c r="M10" t="n">
-        <v>1.34102040741186</v>
+        <v>1.31754276793237</v>
       </c>
       <c r="N10" t="n">
         <v>477.091839631817</v>
@@ -1749,10 +1749,10 @@
         <v>225.602714133335</v>
       </c>
       <c r="T10" t="n">
-        <v>0.00848799712806531</v>
+        <v>0.00833939216593474</v>
       </c>
       <c r="U10" t="n">
-        <v>0.632950630814558</v>
+        <v>0.632950395911765</v>
       </c>
       <c r="V10" t="n">
         <v>0.999884540341955</v>
@@ -1767,13 +1767,13 @@
         <v>784.844</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.000814454516273686</v>
+        <v>0.000800195621032545</v>
       </c>
       <c r="AA10" t="n">
         <v>0.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.32526764396137</v>
+        <v>2.28455849804792</v>
       </c>
       <c r="AC10" t="n">
         <v>70</v>
@@ -1794,7 +1794,7 @@
         <v>45</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.34102040741186</v>
+        <v>1.31754276793237</v>
       </c>
       <c r="AJ10" t="s">
         <v>46</v>
@@ -1818,7 +1818,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.00081</v>
+        <v>0.0008</v>
       </c>
     </row>
   </sheetData>

--- a/data processing/goFlux_reprocessing/ymf_black_oak/results/CO2_best_YMF.xlsx
+++ b/data processing/goFlux_reprocessing/ymf_black_oak/results/CO2_best_YMF.xlsx
@@ -647,7 +647,7 @@
         <v>43</v>
       </c>
       <c r="B2" t="n">
-        <v>1.07119650180274</v>
+        <v>1.05183548735893</v>
       </c>
       <c r="C2" t="n">
         <v>510.673383365281</v>
@@ -668,10 +668,10 @@
         <v>160.072921593051</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00586521027203508</v>
+        <v>0.00575920122764954</v>
       </c>
       <c r="J2" t="n">
-        <v>0.547538221247399</v>
+        <v>0.547538212663887</v>
       </c>
       <c r="K2" t="n">
         <v>0.998592889197321</v>
@@ -680,7 +680,7 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000184169642942053</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12174549713261</v>
+        <v>1.10147085029077</v>
       </c>
       <c r="N2" t="n">
         <v>509.838274465561</v>
@@ -701,10 +701,10 @@
         <v>156.85545936672</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0227208058663035</v>
+        <v>0.0223101452410499</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02548670125105</v>
+        <v>2.02548666949837</v>
       </c>
       <c r="V2" t="n">
         <v>0.998747896186046</v>
@@ -719,19 +719,19 @@
         <v>618.822</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00194804440847494</v>
+        <v>0.00334746137948478</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.28895217995805</v>
+        <v>2.24758121193978</v>
       </c>
       <c r="AC2" t="n">
         <v>48</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.33992765594249</v>
+        <v>1.33710151768142</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -746,7 +746,7 @@
         <v>45</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.12174549713261</v>
+        <v>1.10147085029077</v>
       </c>
       <c r="AJ2" t="s">
         <v>46</v>
@@ -761,7 +761,7 @@
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AO2" t="n">
         <v>2</v>
@@ -770,7 +770,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.0019</v>
+        <v>0.0033</v>
       </c>
     </row>
     <row r="3">
@@ -778,7 +778,7 @@
         <v>48</v>
       </c>
       <c r="B3" t="n">
-        <v>1.2500716114784</v>
+        <v>1.22747757342384</v>
       </c>
       <c r="C3" t="n">
         <v>449.571145105911</v>
@@ -799,10 +799,10 @@
         <v>246.025389037854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00274574398292672</v>
+        <v>0.00269611657624681</v>
       </c>
       <c r="J3" t="n">
-        <v>0.219646935240731</v>
+        <v>0.219646911244695</v>
       </c>
       <c r="K3" t="n">
         <v>0.999633472356177</v>
@@ -811,7 +811,7 @@
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000796761925952472</v>
       </c>
       <c r="M3" t="n">
-        <v>1.30748519423355</v>
+        <v>1.28385345188934</v>
       </c>
       <c r="N3" t="n">
         <v>448.025122126705</v>
@@ -832,10 +832,10 @@
         <v>210.688080667702</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00886322183360238</v>
+        <v>0.00870302528317194</v>
       </c>
       <c r="U3" t="n">
-        <v>0.677883151005622</v>
+        <v>0.67788307694811</v>
       </c>
       <c r="V3" t="n">
         <v>0.99977497116895</v>
@@ -850,19 +850,19 @@
         <v>652.585</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00120803002614691</v>
+        <v>0.00207584274783066</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2892168995484</v>
+        <v>2.24784114693663</v>
       </c>
       <c r="AC3" t="n">
         <v>77</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.7303476829238</v>
+        <v>1.56019867595646</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -877,7 +877,7 @@
         <v>45</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.30748519423355</v>
+        <v>1.28385345188934</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
@@ -892,7 +892,7 @@
         <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AO3" t="n">
         <v>2</v>
@@ -901,7 +901,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0012</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="4">
@@ -909,7 +909,7 @@
         <v>49</v>
       </c>
       <c r="B4" t="n">
-        <v>0.997945522737853</v>
+        <v>0.989737444125356</v>
       </c>
       <c r="C4" t="n">
         <v>570.13579683447</v>
@@ -930,10 +930,10 @@
         <v>745.596707845521</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00256064122916799</v>
+        <v>0.00253957956974029</v>
       </c>
       <c r="J4" t="n">
-        <v>0.256591283875186</v>
+        <v>0.256591238900186</v>
       </c>
       <c r="K4" t="n">
         <v>0.999026524050469</v>
@@ -942,7 +942,7 @@
         <v>1.75082285571673e-223</v>
       </c>
       <c r="M4" t="n">
-        <v>1.10641430554187</v>
+        <v>1.09731407372464</v>
       </c>
       <c r="N4" t="n">
         <v>564.491275687461</v>
@@ -963,10 +963,10 @@
         <v>533.0241986588</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00537187956773167</v>
+        <v>0.00532769504994233</v>
       </c>
       <c r="U4" t="n">
-        <v>0.485521521262398</v>
+        <v>0.485521436160789</v>
       </c>
       <c r="V4" t="n">
         <v>0.999769549580697</v>
@@ -981,19 +981,19 @@
         <v>885.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00062280422235237</v>
+        <v>0.00108094292630142</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.29503355936848</v>
+        <v>2.2761569619547</v>
       </c>
       <c r="AC4" t="n">
         <v>149</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.17414146007619</v>
+        <v>1.24236654861497</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1008,7 +1008,7 @@
         <v>45</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.10641430554187</v>
+        <v>1.09731407372464</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
@@ -1023,7 +1023,7 @@
         <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" t="n">
         <v>2</v>
@@ -1032,7 +1032,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.00062</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="5">
@@ -1040,7 +1040,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1.10579702815972</v>
+        <v>1.08694954002875</v>
       </c>
       <c r="C5" t="n">
         <v>602.085227800366</v>
@@ -1061,10 +1061,10 @@
         <v>325.772821693478</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00692282373586213</v>
+        <v>0.00680482883443247</v>
       </c>
       <c r="J5" t="n">
-        <v>0.62604832166923</v>
+        <v>0.626048273984502</v>
       </c>
       <c r="K5" t="n">
         <v>0.997341812842276</v>
@@ -1073,7 +1073,7 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000313262631310563</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1872653905807</v>
+        <v>1.16702933478796</v>
       </c>
       <c r="N5" t="n">
         <v>600.135154243271</v>
@@ -1094,10 +1094,10 @@
         <v>317.823975957925</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0269980778418222</v>
+        <v>0.0265379136580609</v>
       </c>
       <c r="U5" t="n">
-        <v>2.27397160365445</v>
+        <v>2.27397143045102</v>
       </c>
       <c r="V5" t="n">
         <v>0.997707251307285</v>
@@ -1112,19 +1112,19 @@
         <v>766.692</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00135191427177863</v>
+        <v>0.00232552582190311</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.29149469066478</v>
+        <v>2.25243786750044</v>
       </c>
       <c r="AC5" t="n">
         <v>69</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.41282912996608</v>
+        <v>1.37875950283776</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1139,7 +1139,7 @@
         <v>45</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.1872653905807</v>
+        <v>1.16702933478796</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
@@ -1154,7 +1154,7 @@
         <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1163,7 +1163,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0014</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="6">
@@ -1171,7 +1171,7 @@
         <v>51</v>
       </c>
       <c r="B6" t="n">
-        <v>1.28033394326534</v>
+        <v>1.26551960994157</v>
       </c>
       <c r="C6" t="n">
         <v>475.296879705506</v>
@@ -1192,10 +1192,10 @@
         <v>140.067680438081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00236468560074741</v>
+        <v>0.00233732415493956</v>
       </c>
       <c r="J6" t="n">
-        <v>0.184692877447001</v>
+        <v>0.184692843680825</v>
       </c>
       <c r="K6" t="n">
         <v>0.999791962695814</v>
@@ -1204,7 +1204,7 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000218764550397031</v>
       </c>
       <c r="M6" t="n">
-        <v>1.30069097796678</v>
+        <v>1.28564109992505</v>
       </c>
       <c r="N6" t="n">
         <v>474.856541895539</v>
@@ -1225,10 +1225,10 @@
         <v>141.244244479952</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00939666300834304</v>
+        <v>0.00928793553709479</v>
       </c>
       <c r="U6" t="n">
-        <v>0.722436241007207</v>
+        <v>0.722436108929331</v>
       </c>
       <c r="V6" t="n">
         <v>0.999795764899988</v>
@@ -1243,19 +1243,19 @@
         <v>643.644</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00150861046520551</v>
+        <v>0.0026095209305864</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.29308790711238</v>
+        <v>2.26655532256648</v>
       </c>
       <c r="AC6" t="n">
         <v>62</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.79172451107125</v>
+        <v>1.59527114918357</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1270,7 +1270,7 @@
         <v>45</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.30069097796678</v>
+        <v>1.28564109992505</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
@@ -1285,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1294,7 +1294,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0015</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="7">
@@ -1302,7 +1302,7 @@
         <v>53</v>
       </c>
       <c r="B7" t="n">
-        <v>1.29624180079376</v>
+        <v>1.27853805096221</v>
       </c>
       <c r="C7" t="n">
         <v>543.867877567416</v>
@@ -1323,10 +1323,10 @@
         <v>339.165621088061</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00127786476928609</v>
+        <v>0.00126041182999198</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0985822836837681</v>
+        <v>0.0985822697293536</v>
       </c>
       <c r="K7" t="n">
         <v>0.999887278397298</v>
@@ -1335,7 +1335,7 @@
         <v>4.41442093026646e-229</v>
       </c>
       <c r="M7" t="n">
-        <v>1.31758370670838</v>
+        <v>1.29958847440573</v>
       </c>
       <c r="N7" t="n">
         <v>542.977314137407</v>
@@ -1356,10 +1356,10 @@
         <v>333.717226522434</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00499207298115187</v>
+        <v>0.00492389178640645</v>
       </c>
       <c r="U7" t="n">
-        <v>0.378880898096653</v>
+        <v>0.378880844465632</v>
       </c>
       <c r="V7" t="n">
         <v>0.999894443336438</v>
@@ -1374,19 +1374,19 @@
         <v>868.593</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.000793183693121306</v>
+        <v>0.00136911352632303</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.29230087312057</v>
+        <v>2.26099319489918</v>
       </c>
       <c r="AC7" t="n">
         <v>117</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.82738146635425</v>
+        <v>1.61564655220243</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1401,7 +1401,7 @@
         <v>45</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.31758370670838</v>
+        <v>1.29958847440573</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
@@ -1416,7 +1416,7 @@
         <v>2</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AO7" t="n">
         <v>2</v>
@@ -1425,7 +1425,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.00079</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="8">
@@ -1433,7 +1433,7 @@
         <v>54</v>
       </c>
       <c r="B8" t="n">
-        <v>0.916469315873757</v>
+        <v>0.906185406866212</v>
       </c>
       <c r="C8" t="n">
         <v>536.719264473797</v>
@@ -1454,10 +1454,10 @@
         <v>956.44108841516</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00318230238234952</v>
+        <v>0.00314659313873708</v>
       </c>
       <c r="J8" t="n">
-        <v>0.347235016735452</v>
+        <v>0.347235026617642</v>
       </c>
       <c r="K8" t="n">
         <v>0.998014485619764</v>
@@ -1466,7 +1466,7 @@
         <v>1.00781548562163e-223</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07911649803215</v>
+        <v>1.06700748829</v>
       </c>
       <c r="N8" t="n">
         <v>527.388380071498</v>
@@ -1487,10 +1487,10 @@
         <v>517.809261917687</v>
       </c>
       <c r="T8" t="n">
-        <v>0.00380577528441222</v>
+        <v>0.00376306992821505</v>
       </c>
       <c r="U8" t="n">
-        <v>0.352675108883269</v>
+        <v>0.352675118920281</v>
       </c>
       <c r="V8" t="n">
         <v>0.999860422432155</v>
@@ -1505,19 +1505,19 @@
         <v>857.669</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00055796811463031</v>
+        <v>0.000965487299879778</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.29324895113058</v>
+        <v>2.26751588714622</v>
       </c>
       <c r="AC8" t="n">
         <v>166</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.99818976352728</v>
+        <v>1.14182272201559</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1532,7 +1532,7 @@
         <v>45</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.07911649803215</v>
+        <v>1.06700748829</v>
       </c>
       <c r="AJ8" t="s">
         <v>46</v>
@@ -1547,7 +1547,7 @@
         <v>2</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1556,7 +1556,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00056</v>
+        <v>0.00097</v>
       </c>
     </row>
     <row r="9">
@@ -1564,7 +1564,7 @@
         <v>55</v>
       </c>
       <c r="B9" t="n">
-        <v>1.08136926484062</v>
+        <v>1.06999520481712</v>
       </c>
       <c r="C9" t="n">
         <v>487.872245865154</v>
@@ -1585,10 +1585,10 @@
         <v>1138.39096300744</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00278842047449055</v>
+        <v>0.00275909122627553</v>
       </c>
       <c r="J9" t="n">
-        <v>0.257860156114343</v>
+        <v>0.257860148704788</v>
       </c>
       <c r="K9" t="n">
         <v>0.998731607593589</v>
@@ -1597,7 +1597,7 @@
         <v>2.26349997370336e-277</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2320308651372</v>
+        <v>1.2190721160156</v>
       </c>
       <c r="N9" t="n">
         <v>477.824153577128</v>
@@ -1618,10 +1618,10 @@
         <v>616.154368073799</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00312836337075066</v>
+        <v>0.00309545852492598</v>
       </c>
       <c r="U9" t="n">
-        <v>0.253919236869305</v>
+        <v>0.253919229572991</v>
       </c>
       <c r="V9" t="n">
         <v>0.9999173464781</v>
@@ -1636,19 +1636,19 @@
         <v>926.335</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00048319121426048</v>
+        <v>0.000836690595328864</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.29515826773728</v>
+        <v>2.27101733017835</v>
       </c>
       <c r="AC9" t="n">
         <v>192</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.3557618662758</v>
+        <v>1.34614963787188</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1663,7 +1663,7 @@
         <v>45</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.2320308651372</v>
+        <v>1.2190721160156</v>
       </c>
       <c r="AJ9" t="s">
         <v>46</v>
@@ -1678,7 +1678,7 @@
         <v>2</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AO9" t="n">
         <v>2</v>
@@ -1687,7 +1687,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.00048</v>
+        <v>0.00084</v>
       </c>
     </row>
     <row r="10">
@@ -1695,7 +1695,7 @@
         <v>56</v>
       </c>
       <c r="B10" t="n">
-        <v>1.2386287677836</v>
+        <v>1.21830830268424</v>
       </c>
       <c r="C10" t="n">
         <v>479.164038720243</v>
@@ -1716,10 +1716,10 @@
         <v>286.962165739618</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00252418680633168</v>
+        <v>0.00248277660912308</v>
       </c>
       <c r="J10" t="n">
-        <v>0.203788808397246</v>
+        <v>0.203788860640028</v>
       </c>
       <c r="K10" t="n">
         <v>0.999713524615498</v>
@@ -1728,7 +1728,7 @@
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000203962851563755</v>
       </c>
       <c r="M10" t="n">
-        <v>1.31754276793237</v>
+        <v>1.29592767022994</v>
       </c>
       <c r="N10" t="n">
         <v>477.091839631817</v>
@@ -1749,10 +1749,10 @@
         <v>225.602714133335</v>
       </c>
       <c r="T10" t="n">
-        <v>0.00833939216593474</v>
+        <v>0.00820258142224265</v>
       </c>
       <c r="U10" t="n">
-        <v>0.632950395911765</v>
+        <v>0.6329505581733</v>
       </c>
       <c r="V10" t="n">
         <v>0.999884540341955</v>
@@ -1767,19 +1767,19 @@
         <v>784.844</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.000800195621032545</v>
+        <v>0.00137736886136188</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.28455849804792</v>
+        <v>2.24707891382181</v>
       </c>
       <c r="AC10" t="n">
         <v>70</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.71087120080744</v>
+        <v>1.54906925760425</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -1794,7 +1794,7 @@
         <v>45</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.31754276793237</v>
+        <v>1.29592767022994</v>
       </c>
       <c r="AJ10" t="s">
         <v>46</v>
@@ -1809,7 +1809,7 @@
         <v>2</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -1818,7 +1818,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0008</v>
+        <v>0.0014</v>
       </c>
     </row>
   </sheetData>

--- a/data processing/goFlux_reprocessing/ymf_black_oak/results/CO2_best_YMF.xlsx
+++ b/data processing/goFlux_reprocessing/ymf_black_oak/results/CO2_best_YMF.xlsx
@@ -146,22 +146,22 @@
     <t xml:space="preserve">YMF_0.5m</t>
   </si>
   <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YMF_1.25m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YMF_10m</t>
+  </si>
+  <si>
     <t xml:space="preserve">Noise (HM.MAE)</t>
   </si>
   <si>
     <t xml:space="preserve">Noise (LM.MAE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">YMF_1.25m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YMF_10m</t>
   </si>
   <si>
     <t xml:space="preserve">YMF_2m</t>
@@ -719,10 +719,10 @@
         <v>618.822</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00334746137948478</v>
+        <v>0.0103194294544325</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AB2" t="n">
         <v>2.24758121193978</v>
@@ -731,7 +731,7 @@
         <v>48</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.33710151768142</v>
+        <v>0.426475642107002</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -743,16 +743,16 @@
         <v>44</v>
       </c>
       <c r="AH2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI2" t="n">
         <v>1.10147085029077</v>
       </c>
       <c r="AJ2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AO2" t="n">
         <v>2</v>
@@ -770,12 +770,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.0033</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B3" t="n">
         <v>1.22747757342384</v>
@@ -850,10 +850,10 @@
         <v>652.585</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00207584274783066</v>
+        <v>0.006440284268141</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AB3" t="n">
         <v>2.24784114693663</v>
@@ -862,7 +862,7 @@
         <v>77</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.56019867595646</v>
+        <v>0.497633667559385</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -874,16 +874,16 @@
         <v>44</v>
       </c>
       <c r="AH3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI3" t="n">
         <v>1.28385345188934</v>
       </c>
       <c r="AJ3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -892,7 +892,7 @@
         <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AO3" t="n">
         <v>2</v>
@@ -901,12 +901,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0021</v>
+        <v>0.0064</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B4" t="n">
         <v>0.989737444125356</v>
@@ -981,10 +981,10 @@
         <v>885.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00108094292630142</v>
+        <v>0.00337071624206704</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AB4" t="n">
         <v>2.2761569619547</v>
@@ -993,7 +993,7 @@
         <v>149</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24236654861497</v>
+        <v>0.396259419757138</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1002,19 +1002,19 @@
         <v>1.10869208822785</v>
       </c>
       <c r="AG4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AI4" t="n">
         <v>1.09731407372464</v>
       </c>
       <c r="AJ4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1023,7 +1023,7 @@
         <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AO4" t="n">
         <v>2</v>
@@ -1032,7 +1032,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0011</v>
+        <v>0.0034</v>
       </c>
     </row>
     <row r="5">
@@ -1112,10 +1112,10 @@
         <v>766.692</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00232552582190311</v>
+        <v>0.00720604374639235</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AB5" t="n">
         <v>2.25243786750044</v>
@@ -1124,7 +1124,7 @@
         <v>69</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.37875950283776</v>
+        <v>0.43976267808258</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1133,19 +1133,19 @@
         <v>1.07367388439862</v>
       </c>
       <c r="AG5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AI5" t="n">
         <v>1.16702933478796</v>
       </c>
       <c r="AJ5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1154,7 +1154,7 @@
         <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1163,7 +1163,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0023</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="6">
@@ -1243,10 +1243,10 @@
         <v>643.644</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0026095209305864</v>
+        <v>0.00807520956355155</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AB6" t="n">
         <v>2.26655532256648</v>
@@ -1255,7 +1255,7 @@
         <v>62</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.59527114918357</v>
+        <v>0.508820219471876</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1267,13 +1267,13 @@
         <v>44</v>
       </c>
       <c r="AH6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI6" t="n">
         <v>1.28564109992505</v>
       </c>
       <c r="AJ6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK6" t="s">
         <v>52</v>
@@ -1285,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1294,7 +1294,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0026</v>
+        <v>0.0081</v>
       </c>
     </row>
     <row r="7">
@@ -1374,10 +1374,10 @@
         <v>868.593</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00136911352632303</v>
+        <v>0.00426299148244874</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AB7" t="n">
         <v>2.26099319489918</v>
@@ -1386,7 +1386,7 @@
         <v>117</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.61564655220243</v>
+        <v>0.51531906265674</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1398,16 +1398,16 @@
         <v>44</v>
       </c>
       <c r="AH7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI7" t="n">
         <v>1.29958847440573</v>
       </c>
       <c r="AJ7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>2</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AO7" t="n">
         <v>2</v>
@@ -1425,7 +1425,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0014</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="8">
@@ -1505,10 +1505,10 @@
         <v>857.669</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.000965487299879778</v>
+        <v>0.00301237119151321</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AB8" t="n">
         <v>2.26751588714622</v>
@@ -1517,7 +1517,7 @@
         <v>166</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14182272201559</v>
+        <v>0.364190431395491</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1529,16 +1529,16 @@
         <v>44</v>
       </c>
       <c r="AH8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AI8" t="n">
         <v>1.06700748829</v>
       </c>
       <c r="AJ8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1547,7 +1547,7 @@
         <v>2</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1556,7 +1556,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00097</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="9">
@@ -1636,10 +1636,10 @@
         <v>926.335</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.000836690595328864</v>
+        <v>0.00261222311426031</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AB9" t="n">
         <v>2.27101733017835</v>
@@ -1648,7 +1648,7 @@
         <v>192</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.34614963787188</v>
+        <v>0.429361588175465</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1660,16 +1660,16 @@
         <v>44</v>
       </c>
       <c r="AH9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AI9" t="n">
         <v>1.2190721160156</v>
       </c>
       <c r="AJ9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>2</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AO9" t="n">
         <v>2</v>
@@ -1687,7 +1687,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.00084</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="10">
@@ -1767,10 +1767,10 @@
         <v>784.844</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.00137736886136188</v>
+        <v>0.00428833469847012</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AB10" t="n">
         <v>2.24707891382181</v>
@@ -1779,7 +1779,7 @@
         <v>70</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.54906925760425</v>
+        <v>0.494083880370251</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -1791,16 +1791,16 @@
         <v>44</v>
       </c>
       <c r="AH10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AI10" t="n">
         <v>1.29592767022994</v>
       </c>
       <c r="AJ10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -1809,7 +1809,7 @@
         <v>2</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.35</v>
+        <v>1.09733237958542</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -1818,7 +1818,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0014</v>
+        <v>0.0043</v>
       </c>
     </row>
   </sheetData>
